--- a/utils/data-room-simulator/output/tenure_analysis.xlsx
+++ b/utils/data-room-simulator/output/tenure_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tenure" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tenure" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tenure_band</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>headcount</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>avg_salary</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_of_total</t>
         </is>
@@ -457,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>135587.07</v>
+        <v>86373</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>152643.96</v>
+        <v>83069.67</v>
       </c>
       <c r="D3" t="n">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>169497.4</v>
+        <v>79133.74000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>12.1</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +493,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" t="n">
-        <v>172001.37</v>
+        <v>97079.10000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>34.8</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +509,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6" t="n">
-        <v>214500.37</v>
+        <v>116233.79</v>
       </c>
       <c r="D6" t="n">
-        <v>28.8</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +528,10 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>299887.26</v>
+        <v>136805.01</v>
       </c>
       <c r="D7" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
